--- a/resources/templates/contract/智书合同字段-一般流程.xlsx
+++ b/resources/templates/contract/智书合同字段-一般流程.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="26505" windowHeight="17055" tabRatio="782" firstSheet="2"/>
+    <workbookView windowHeight="17655" tabRatio="782" firstSheet="2"/>
   </bookViews>
   <sheets>
     <sheet name="字段模板" sheetId="1" r:id="rId1"/>
@@ -14,12 +14,12 @@
     <sheet name="采购申请" sheetId="5" r:id="rId5"/>
     <sheet name="订单信息明细" sheetId="6" r:id="rId6"/>
     <sheet name="对方信息" sheetId="7" r:id="rId7"/>
-    <sheet name="我方主体列表" sheetId="9" r:id="rId8"/>
-    <sheet name="付款计划" sheetId="10" r:id="rId9"/>
-    <sheet name="收款计划" sheetId="12" r:id="rId10"/>
-    <sheet name="合同附件" sheetId="14" r:id="rId11"/>
-    <sheet name="其他附件" sheetId="15" r:id="rId12"/>
-    <sheet name="DropdownOptions" sheetId="16" r:id="rId13"/>
+    <sheet name="我方主体列表" sheetId="8" r:id="rId8"/>
+    <sheet name="付款计划" sheetId="9" r:id="rId9"/>
+    <sheet name="收款计划" sheetId="10" r:id="rId10"/>
+    <sheet name="合同附件" sheetId="11" r:id="rId11"/>
+    <sheet name="其他附件" sheetId="12" r:id="rId12"/>
+    <sheet name="DropdownOptions" sheetId="13" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="DV_1">选项!$A$1:$A$4</definedName>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="205">
   <si>
     <t>contract_number（合同编码）</t>
   </si>
@@ -69,12 +69,21 @@
     <t>contract_name（合同名称）</t>
   </si>
   <si>
+    <t>泛微项目编码</t>
+  </si>
+  <si>
     <t>合同审批状态</t>
   </si>
   <si>
     <t>contractCategory(智书框架合同类型)</t>
   </si>
   <si>
+    <t>收入币种</t>
+  </si>
+  <si>
+    <t>支出币种</t>
+  </si>
+  <si>
     <t>订单编号</t>
   </si>
   <si>
@@ -114,26 +123,7 @@
     <t>remark（合同说明）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>custom_1001_948719050bfe402ab083c98e52fa71b2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（合同执行人）飞书user_id</t>
-    </r>
+    <t>custom_1001_948719050bfe402ab083c98e52fa71b2（合同执行人）飞书user_id</t>
   </si>
   <si>
     <t>合同执行人</t>
@@ -166,92 +156,16 @@
     <t>custom_15_e5f7b7cb17b34602adf790f0ac8d69a1（发票种类）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>custom_15_7b0d0e2f63a148729f929ba985c227c2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（收入税率）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>custom_15_b293866468ac4ab4bb11b5cb8c9bbb37</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（收入税目）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>custom_15_7b0d0e2f63a148729f929ba985c227c2</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（支出税率）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>custom_15_b293866468ac4ab4bb11b5cb8c9bbb37</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（支出税目）</t>
-    </r>
+    <t>custom_15_7b0d0e2f63a148729f929ba985c227c2（收入税率）</t>
+  </si>
+  <si>
+    <t>custom_15_b293866468ac4ab4bb11b5cb8c9bbb37（收入税目）</t>
+  </si>
+  <si>
+    <t>custom_15_7b0d0e2f63a148729f929ba985c227c2（支出税率）</t>
+  </si>
+  <si>
+    <t>custom_15_b293866468ac4ab4bb11b5cb8c9bbb37（支出税目）</t>
   </si>
   <si>
     <t>custom_15_e46e1f9b6eb0469987f0656a999cdf09（银行手续费承担方）</t>
@@ -260,70 +174,13 @@
     <t>custom_1012_7e2c970e63f648268eaefbd13d6bfc8f（押金/保证金）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>sign_type_code</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（先盖章方）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>sign_type_code</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（签约形式）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>seal_number</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（盖章份数）待确认必填项</t>
-    </r>
+    <t>sign_type_code（先盖章方）</t>
+  </si>
+  <si>
+    <t>sign_type_code（签约形式）</t>
+  </si>
+  <si>
+    <t>seal_number（盖章份数）待确认必填项</t>
   </si>
   <si>
     <t>contract_files.contract_text（合同文本）</t>
@@ -761,38 +618,7 @@
     <t>custom_1001_8b8028ca466f4841bead801a9c7fedf2（项目预算岗）飞书user_id</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>custom_1001_9072dcb2126e4051854da3927f742ab9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（项目</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>Sponsor-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>项目经理B）飞书user_id</t>
-    </r>
+    <t>custom_1001_9072dcb2126e4051854da3927f742ab9（项目Sponsor-项目经理B）飞书user_id</t>
   </si>
   <si>
     <t>custom_15_622e96ab047c4f689d287a27066f7bcb（订单类型）</t>
@@ -825,46 +651,7 @@
     <t>payment_plan_list[].payment_counter_party[].counter_party_code（付款对象）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>付款计划行</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>id(</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>付款记录传的</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>id)</t>
-    </r>
+    <t>付款计划行id(付款记录传的id)</t>
   </si>
   <si>
     <t>collection_plan_list（收款计划）</t>
@@ -882,40 +669,7 @@
     <t>collection_plan_list[].collection_counter_party[].counter_party_code（收款对象）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>收款计划行</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>id(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>收款记录传的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>id)</t>
-    </r>
+    <t>收款计划行id(收款记录传的id)</t>
   </si>
   <si>
     <t>contract_files.contract_causes（合同附件）</t>
@@ -1447,152 +1201,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1603,16 +1357,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1932,50 +1683,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AN2"/>
+  <dimension ref="A1:AQ2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="40" width="32" customWidth="1"/>
+    <col min="1" max="2" width="32" customWidth="1"/>
+    <col min="3" max="4" width="13" customWidth="1"/>
+    <col min="5" max="42" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="58.5" customHeight="1" spans="1:40">
+    <row r="1" ht="58.5" customHeight="1" spans="1:43">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="1" t="s">
@@ -1993,40 +1746,40 @@
       <c r="R1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="W1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="5" t="s">
         <v>23</v>
       </c>
       <c r="Y1" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AA1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
       <c r="AC1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
       <c r="AE1" s="1" t="s">
@@ -2038,7 +1791,7 @@
       <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AH1" s="1" t="s">
         <v>33</v>
       </c>
       <c r="AI1" s="1" t="s">
@@ -2047,59 +1800,68 @@
       <c r="AJ1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AK1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AM1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AN1" s="1" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="2" spans="1:40">
-      <c r="Y2" s="7"/>
+      <c r="AO1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:43">
+      <c r="AB2" s="6"/>
     </row>
   </sheetData>
   <dataValidations count="13">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y1 AB1"/>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F1048576">
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AA1 AD1"/>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F1048576 G2:G1048576 H2:H1048576">
       <formula1>DV_1</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="I2:I1048576">
       <formula1>DV_2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N2:N1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="P2:P1048576">
       <formula1>DV_3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R2:R1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="T2:T1048576">
       <formula1>DV_4</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y2:Y1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA2:AA1048576">
       <formula1>DropdownOptions!$A$1:$A$56</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z2:Z1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AB2:AB1048576">
       <formula1>DV_9</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB2:AB1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AD2:AD1048576">
       <formula1>"增值税专用发票,invoice,普通发票,专用发票"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AC2:AC1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AE2:AE1048576">
       <formula1>DropdownOptions!$C$1:$C$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG2:AG1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI2:AI1048576">
       <formula1>"对方承担,各自承担,我方承担"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AI2:AI1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AK2:AK1048576">
       <formula1>DV_14</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ2:AJ1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AL2:AL1048576">
       <formula1>"纸质签约,中国大陆电子签（e签宝）,非中国大陆电子签（Docusign）"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AD2:AF1048576">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AF2:AH1048576">
       <formula1>DropdownOptions!$B$1:$B$20</formula1>
     </dataValidation>
   </dataValidations>
@@ -2124,22 +1886,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -2162,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
   </sheetData>
@@ -2185,7 +1947,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -2207,357 +1969,357 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B11" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B17" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B18" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B19" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B20" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2574,525 +2336,525 @@
   <sheetData>
     <row r="1" spans="1:20">
       <c r="A1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F1" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="H1" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="I1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J1" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K1" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O1" t="s">
+        <v>57</v>
+      </c>
+      <c r="P1" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R1" t="s">
         <v>50</v>
       </c>
-      <c r="L1" t="s">
-        <v>51</v>
-      </c>
-      <c r="M1" t="s">
-        <v>52</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="S1" t="s">
+        <v>59</v>
+      </c>
+      <c r="T1" t="s">
         <v>53</v>
-      </c>
-      <c r="O1" t="s">
-        <v>54</v>
-      </c>
-      <c r="P1" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>55</v>
-      </c>
-      <c r="R1" t="s">
-        <v>47</v>
-      </c>
-      <c r="S1" t="s">
-        <v>56</v>
-      </c>
-      <c r="T1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:20">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="D2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="N2" t="s">
+        <v>70</v>
+      </c>
+      <c r="O2" t="s">
+        <v>71</v>
+      </c>
+      <c r="P2" t="s">
         <v>67</v>
       </c>
-      <c r="O2" t="s">
-        <v>68</v>
-      </c>
-      <c r="P2" t="s">
-        <v>64</v>
-      </c>
       <c r="Q2" t="s">
+        <v>72</v>
+      </c>
+      <c r="R2" t="s">
+        <v>73</v>
+      </c>
+      <c r="S2" t="s">
         <v>69</v>
       </c>
-      <c r="R2" t="s">
-        <v>70</v>
-      </c>
-      <c r="S2" t="s">
-        <v>66</v>
-      </c>
       <c r="T2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:20">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="F3" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="O3" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="R3" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="S3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="T3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:20">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="R4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="S4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="T4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:20">
       <c r="F5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="O5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="R5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="S5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="T5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:20">
       <c r="F6" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="O6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="R6" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="S6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="F7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="O7" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="R7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="S7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="F8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="O8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="R8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="S8" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="O9" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="R9" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="S9" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="O10" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="R10" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="S10" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="O11" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="R11" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="S11" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="O12" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="R12" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="S12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:20">
       <c r="O13" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="R13" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="S13" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:20">
       <c r="O14" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="R14" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="S14" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:20">
       <c r="O15" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="R15" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="S15" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="O16" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="R16" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="S16" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="15:19">
       <c r="O17" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="R17" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="S17" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="15:19">
       <c r="O18" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="R18" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="S18" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="15:19">
       <c r="R19" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="S19" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="15:19">
       <c r="R20" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="S20" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21" spans="15:19">
       <c r="R21" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="22" spans="15:19">
       <c r="R22" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="15:19">
       <c r="R23" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="15:19">
       <c r="R24" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="15:19">
       <c r="R25" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="15:19">
       <c r="R26" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="15:19">
       <c r="R27" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="15:19">
       <c r="R28" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="15:19">
       <c r="R29" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="30" spans="15:19">
       <c r="R30" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="31" spans="15:19">
       <c r="R31" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32" spans="15:19">
       <c r="R32" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="18:18">
       <c r="R33" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34" spans="18:18">
       <c r="R34" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="18:18">
       <c r="R35" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="36" spans="18:18">
       <c r="R36" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="37" spans="18:18">
       <c r="R37" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="38" spans="18:18">
       <c r="R38" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="39" spans="18:18">
       <c r="R39" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="40" spans="18:18">
       <c r="R40" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="41" spans="18:18">
       <c r="R41" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="42" spans="18:18">
       <c r="R42" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
     </row>
     <row r="43" spans="18:18">
       <c r="R43" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" spans="18:18">
       <c r="R44" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="18:18">
       <c r="R45" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" spans="18:18">
       <c r="R46" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="47" spans="18:18">
       <c r="R47" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="48" spans="18:18">
       <c r="R48" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
     </row>
     <row r="49" spans="18:18">
       <c r="R49" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="50" spans="18:18">
       <c r="R50" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="51" spans="18:18">
       <c r="R51" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="18:18">
       <c r="R52" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="53" spans="18:18">
       <c r="R53" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="54" spans="18:18">
       <c r="R54" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="55" spans="18:18">
       <c r="R55" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="56" spans="18:18">
       <c r="R56" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -3117,10 +2879,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -3143,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3166,7 +2928,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -3189,34 +2951,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>182</v>
+        <v>184</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>185</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -3250,7 +3012,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -3274,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
@@ -3299,28 +3061,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
